--- a/multilingual/多语言表格模板.xlsx
+++ b/multilingual/多语言表格模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="145">
   <si>
     <t>ID</t>
   </si>
@@ -68,12 +68,18 @@
     <t>繁体中文</t>
   </si>
   <si>
+    <t>注释</t>
+  </si>
+  <si>
     <t>key</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>none</t>
+  </si>
+  <si>
     <t>确定</t>
   </si>
   <si>
@@ -204,6 +210,42 @@
   </si>
   <si>
     <t>開始遊戲</t>
+  </si>
+  <si>
+    <t>开始</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Играть</t>
+  </si>
+  <si>
+    <t>Jugar</t>
+  </si>
+  <si>
+    <t>Jogar</t>
+  </si>
+  <si>
+    <t>Jouer</t>
+  </si>
+  <si>
+    <t>スタート</t>
+  </si>
+  <si>
+    <t>시작</t>
+  </si>
+  <si>
+    <t>Graj</t>
+  </si>
+  <si>
+    <t>Başla</t>
+  </si>
+  <si>
+    <t>開始</t>
+  </si>
+  <si>
+    <t>当某些文本非常短，单独看十分难明白是什么意思的时候，需要增加注释，说明该词语的使用环境或者实际含义，例如这里的“开始”表示游戏开始的意思</t>
   </si>
   <si>
     <t>游戏暂停</t>
@@ -1602,7 +1644,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
@@ -1610,7 +1652,7 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1650,456 +1692,506 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>43</v>
-      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
